--- a/src/Thông tin HKD.xlsx
+++ b/src/Thông tin HKD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEVELOPER\3.accounting_excel\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDA5DAA-B7A6-4774-ADA1-9C64A3E0AF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D70D98-D50F-4418-B349-32076591BE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,6 +31,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
+    <author>Admin</author>
   </authors>
   <commentList>
     <comment ref="R3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -81,6 +82,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="C17" authorId="1" shapeId="0" xr:uid="{B65EDCB4-C5AB-4B8E-BDAC-219B2D62BDDA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Sao kê có vẻ bị thiếu</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="1" shapeId="0" xr:uid="{03672AE1-88CC-4081-AE40-7760DEC91C87}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Không phát sinh giao dịch</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
   <extLst>
     <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion2">
@@ -91,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="241">
   <si>
     <t>STT</t>
   </si>
@@ -812,6 +861,9 @@
   <si>
     <t>Tiến độ</t>
   </si>
+  <si>
+    <t>066194015688</t>
+  </si>
 </sst>
 </file>
 
@@ -821,7 +873,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="165" formatCode="dd&quot;/&quot;mm&quot;/&quot;yy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -929,6 +981,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1008,11 +1073,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1035,26 +1095,7 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1063,7 +1104,31 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1310,8 +1375,14 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="E1" s="1">
+        <f>COUNTIF(E$4:E$42,"v")</f>
+        <v>28</v>
+      </c>
+      <c r="F1" s="1">
+        <f>COUNTIF(F$4:F$42,"v")</f>
+        <v>23</v>
+      </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="2"/>
@@ -1341,16 +1412,16 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="63">
-        <f>COUNTIF(E$4:E$42,"v")/(MAX($A$4:$A$42)-COUNTIF(E$4:E$42,"-"))</f>
-        <v>0.21052631578947367</v>
-      </c>
-      <c r="F2" s="63">
-        <f>COUNTIF(F$4:F$42,"v")/(MAX($A$4:$A$42)-COUNTIF(F$4:F$42,"-"))</f>
-        <v>0.21052631578947367</v>
+      <c r="E2" s="47">
+        <f>E1/(MAX($A$4:$A$42)-COUNTIF(E$4:E$42,"-"))</f>
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="F2" s="47">
+        <f>F1/(MAX($A$4:$A$42)-COUNTIF(F$4:F$42,"-"))</f>
+        <v>0.6216216216216216</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1381,13 +1452,13 @@
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="61" t="s">
+      <c r="C3" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="41" t="s">
         <v>236</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -1461,549 +1532,557 @@
       <c r="AC3" s="6"/>
       <c r="AD3" s="7"/>
     </row>
-    <row r="4" spans="1:31" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="G4" s="42" t="s">
+      <c r="G4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="49" t="s">
+      <c r="K4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="43" t="s">
+      <c r="L4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="49" t="s">
+      <c r="N4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="54" t="s">
+      <c r="O4" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="42" t="s">
+      <c r="P4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q4" s="44">
+      <c r="Q4" s="10">
         <v>3</v>
       </c>
-      <c r="R4" s="44">
+      <c r="R4" s="10">
         <v>690300</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="15">
         <v>45839</v>
       </c>
-      <c r="T4" s="42" t="s">
+      <c r="T4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="45"/>
-      <c r="V4" s="42" t="s">
+      <c r="U4" s="11"/>
+      <c r="V4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="44"/>
-      <c r="X4" s="51" t="s">
+      <c r="W4" s="10"/>
+      <c r="X4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" s="42" t="s">
+      <c r="Y4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="46"/>
-      <c r="AC4" s="46"/>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="47"/>
-    </row>
-    <row r="5" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+    </row>
+    <row r="5" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
         <f t="shared" ref="A5:A42" si="0">+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="28" t="s">
+      <c r="B5" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="28" t="s">
+      <c r="K5" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="M5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N5" s="28" t="s">
+      <c r="N5" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="57" t="s">
+      <c r="O5" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="28" t="s">
+      <c r="P5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="30">
+      <c r="Q5" s="25">
         <v>3</v>
       </c>
-      <c r="R5" s="30">
+      <c r="R5" s="25">
         <v>690300</v>
       </c>
-      <c r="S5" s="31">
+      <c r="S5" s="26">
         <v>45839</v>
       </c>
-      <c r="T5" s="28" t="s">
+      <c r="T5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="32"/>
-      <c r="V5" s="28" t="s">
+      <c r="U5" s="27"/>
+      <c r="V5" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="W5" s="30"/>
-      <c r="X5" s="37" t="s">
+      <c r="W5" s="25"/>
+      <c r="X5" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="Y5" s="28" t="s">
+      <c r="Y5" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="34"/>
-      <c r="AE5" s="34"/>
-    </row>
-    <row r="6" spans="1:31" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41">
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="29"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="41" t="s">
+      <c r="J6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="43" t="s">
+      <c r="L6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="42" t="s">
+      <c r="M6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="42" t="s">
+      <c r="N6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="55" t="s">
+      <c r="O6" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="42" t="s">
+      <c r="P6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q6" s="44">
+      <c r="Q6" s="10">
         <v>3</v>
       </c>
-      <c r="R6" s="44">
+      <c r="R6" s="10">
         <v>690300</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="15">
         <v>45839</v>
       </c>
-      <c r="T6" s="42" t="s">
+      <c r="T6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="U6" s="45"/>
-      <c r="V6" s="42" t="s">
+      <c r="U6" s="11"/>
+      <c r="V6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="W6" s="44"/>
-      <c r="X6" s="51" t="s">
+      <c r="W6" s="10"/>
+      <c r="X6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="Y6" s="42" t="s">
+      <c r="Y6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="46"/>
-      <c r="AB6" s="46"/>
-      <c r="AC6" s="46"/>
-      <c r="AD6" s="47"/>
-      <c r="AE6" s="47"/>
-    </row>
-    <row r="7" spans="1:31" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="41">
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="56" t="s">
+      <c r="D7" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G7" s="42" t="s">
+      <c r="G7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="42" t="s">
+      <c r="K7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="43" t="s">
+      <c r="L7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M7" s="42" t="s">
+      <c r="M7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N7" s="42" t="s">
+      <c r="N7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O7" s="43" t="s">
+      <c r="O7" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="42" t="s">
+      <c r="P7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q7" s="44">
+      <c r="Q7" s="10">
         <v>3</v>
       </c>
-      <c r="R7" s="44">
+      <c r="R7" s="10">
         <v>2950000</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="15">
         <v>45839</v>
       </c>
-      <c r="T7" s="42" t="s">
+      <c r="T7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="U7" s="45"/>
-      <c r="V7" s="45"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="53" t="s">
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="Y7" s="42" t="s">
+      <c r="Y7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="47"/>
-      <c r="AE7" s="47"/>
-    </row>
-    <row r="8" spans="1:31" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41">
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="56" t="s">
+      <c r="B8" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D8" s="56" t="s">
+      <c r="D8" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G8" s="42" t="s">
+      <c r="G8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="52" t="s">
+      <c r="H8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="42" t="s">
+      <c r="K8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="43" t="s">
+      <c r="L8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M8" s="42" t="s">
+      <c r="M8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="42" t="s">
+      <c r="N8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="43" t="s">
+      <c r="O8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="42" t="s">
+      <c r="P8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q8" s="44">
+      <c r="Q8" s="10">
         <v>3</v>
       </c>
-      <c r="R8" s="44">
+      <c r="R8" s="10">
         <v>690300</v>
       </c>
-      <c r="S8" s="50">
+      <c r="S8" s="15">
         <v>45839</v>
       </c>
-      <c r="T8" s="42" t="s">
+      <c r="T8" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="U8" s="45"/>
-      <c r="V8" s="42" t="s">
+      <c r="U8" s="11"/>
+      <c r="V8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="W8" s="44"/>
-      <c r="X8" s="53" t="s">
+      <c r="W8" s="10"/>
+      <c r="X8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="Y8" s="42" t="s">
+      <c r="Y8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="Z8" s="42"/>
-      <c r="AA8" s="46"/>
-      <c r="AB8" s="46"/>
-      <c r="AC8" s="46"/>
-      <c r="AD8" s="47"/>
-      <c r="AE8" s="47"/>
-    </row>
-    <row r="9" spans="1:31" s="48" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41">
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G9" s="42" t="s">
+      <c r="G9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="52" t="s">
+      <c r="H9" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="42" t="s">
+      <c r="K9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="43" t="s">
+      <c r="L9" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="42" t="s">
+      <c r="M9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="42" t="s">
+      <c r="N9" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="44">
+      <c r="O9" s="9"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="10">
         <v>3</v>
       </c>
-      <c r="R9" s="44"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="42" t="s">
+      <c r="R9" s="10"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="U9" s="45"/>
-      <c r="V9" s="42" t="s">
+      <c r="U9" s="11"/>
+      <c r="V9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="W9" s="44"/>
-      <c r="X9" s="53" t="s">
+      <c r="W9" s="10"/>
+      <c r="X9" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="Y9" s="42" t="s">
+      <c r="Y9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="46"/>
-      <c r="AB9" s="46"/>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="47"/>
-      <c r="AE9" s="47"/>
-    </row>
-    <row r="10" spans="1:31" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27">
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+    </row>
+    <row r="10" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="22">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28" t="s">
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="I10" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="J10" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="28" t="s">
+      <c r="K10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="28" t="s">
+      <c r="M10" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="28" t="s">
+      <c r="N10" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="O10" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="P10" s="28" t="s">
+      <c r="P10" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q10" s="30">
+      <c r="Q10" s="25">
         <v>3</v>
       </c>
-      <c r="R10" s="30">
+      <c r="R10" s="25">
         <v>690300</v>
       </c>
-      <c r="S10" s="31">
+      <c r="S10" s="26">
         <v>45839</v>
       </c>
-      <c r="T10" s="28" t="s">
+      <c r="T10" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="U10" s="32"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="37" t="s">
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="Y10" s="28" t="s">
+      <c r="Y10" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="34"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="56" t="s">
+      <c r="C11" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="D11" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G11" s="8" t="s">
         <v>70</v>
       </c>
@@ -2019,7 +2098,7 @@
       <c r="K11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="48" t="s">
         <v>72</v>
       </c>
       <c r="M11" s="8" t="s">
@@ -2069,19 +2148,19 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="34" t="s">
         <v>219</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="34" t="s">
         <v>219</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -2149,19 +2228,19 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D13" s="56" t="s">
+      <c r="D13" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="34" t="s">
         <v>219</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -2229,19 +2308,19 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="34" t="s">
         <v>219</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -2309,17 +2388,21 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D15" s="56" t="s">
+      <c r="D15" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="39"/>
-      <c r="F15" s="13"/>
+      <c r="E15" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G15" s="8" t="s">
         <v>98</v>
       </c>
@@ -2385,17 +2468,21 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G16" s="8" t="s">
         <v>105</v>
       </c>
@@ -2456,98 +2543,106 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+    <row r="17" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="8" t="s">
+      <c r="E17" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="G17" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="M17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="N17" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O17" s="19" t="s">
+      <c r="O17" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="P17" s="8" t="s">
+      <c r="P17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="Q17" s="25">
         <v>3</v>
       </c>
-      <c r="R17" s="10">
+      <c r="R17" s="25">
         <v>690300</v>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="26">
         <v>45839</v>
       </c>
-      <c r="T17" s="8" t="s">
+      <c r="T17" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="U17" s="11"/>
-      <c r="V17" s="8" t="s">
+      <c r="U17" s="27"/>
+      <c r="V17" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="W17" s="10"/>
-      <c r="X17" s="18" t="s">
+      <c r="W17" s="25"/>
+      <c r="X17" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="Y17" s="8" t="s">
+      <c r="Y17" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="Z17" s="8"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="4"/>
-      <c r="AE17" s="4"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
     </row>
     <row r="18" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
+      <c r="E18" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G18" s="8" t="s">
         <v>119</v>
       </c>
@@ -2595,7 +2690,7 @@
         <v>25</v>
       </c>
       <c r="W18" s="10"/>
-      <c r="X18" s="20" t="s">
+      <c r="X18" s="43" t="s">
         <v>123</v>
       </c>
       <c r="Y18" s="8" t="s">
@@ -2608,77 +2703,77 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
     </row>
-    <row r="19" spans="1:31" s="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="27">
+    <row r="19" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28" t="s">
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="H19" s="36" t="s">
+      <c r="H19" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="I19" s="27" t="s">
+      <c r="I19" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="27" t="s">
+      <c r="J19" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K19" s="28" t="s">
+      <c r="K19" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L19" s="29" t="s">
+      <c r="L19" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="M19" s="28" t="s">
+      <c r="M19" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N19" s="28" t="s">
+      <c r="N19" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O19" s="29" t="s">
+      <c r="O19" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="P19" s="28" t="s">
+      <c r="P19" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q19" s="30">
+      <c r="Q19" s="25">
         <v>3</v>
       </c>
-      <c r="R19" s="30">
+      <c r="R19" s="25">
         <v>690300</v>
       </c>
-      <c r="S19" s="31">
+      <c r="S19" s="26">
         <v>45870</v>
       </c>
-      <c r="T19" s="28" t="s">
+      <c r="T19" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="U19" s="32"/>
-      <c r="V19" s="28" t="s">
+      <c r="U19" s="27"/>
+      <c r="V19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="W19" s="30"/>
-      <c r="X19" s="37" t="s">
+      <c r="W19" s="25"/>
+      <c r="X19" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="Y19" s="28" t="s">
+      <c r="Y19" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="34"/>
+      <c r="Z19" s="23"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="29"/>
     </row>
     <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
@@ -2688,14 +2783,18 @@
       <c r="B20" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="39" t="s">
+      <c r="C20" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D20" s="56" t="s">
+      <c r="D20" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G20" s="8" t="s">
         <v>131</v>
       </c>
@@ -2764,14 +2863,18 @@
       <c r="B21" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
+      <c r="E21" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G21" s="8" t="s">
         <v>137</v>
       </c>
@@ -2838,14 +2941,18 @@
       <c r="B22" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
+      <c r="E22" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G22" s="8" t="s">
         <v>143</v>
       </c>
@@ -2914,14 +3021,18 @@
       <c r="B23" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D23" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="E23" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G23" s="8" t="s">
         <v>149</v>
       </c>
@@ -2990,14 +3101,18 @@
       <c r="B24" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="E24" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G24" s="8" t="s">
         <v>155</v>
       </c>
@@ -3045,7 +3160,7 @@
         <v>25</v>
       </c>
       <c r="W24" s="10"/>
-      <c r="X24" s="21" t="s">
+      <c r="X24" s="44" t="s">
         <v>158</v>
       </c>
       <c r="Y24" s="8" t="s">
@@ -3058,75 +3173,75 @@
       <c r="AD24" s="4"/>
       <c r="AE24" s="4"/>
     </row>
-    <row r="25" spans="1:31" s="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27">
+    <row r="25" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="28" t="s">
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="36" t="s">
+      <c r="H25" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="I25" s="27" t="s">
+      <c r="I25" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="27" t="s">
+      <c r="J25" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K25" s="28" t="s">
+      <c r="K25" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L25" s="29" t="s">
+      <c r="L25" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="M25" s="28" t="s">
+      <c r="M25" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N25" s="28" t="s">
+      <c r="N25" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O25" s="29" t="s">
+      <c r="O25" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="P25" s="28" t="s">
+      <c r="P25" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="25">
         <v>3</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="25">
         <v>5900000</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="26">
         <v>45931</v>
       </c>
-      <c r="T25" s="28" t="s">
+      <c r="T25" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="U25" s="32"/>
-      <c r="V25" s="28" t="s">
+      <c r="U25" s="27"/>
+      <c r="V25" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="W25" s="30"/>
-      <c r="X25" s="58" t="s">
+      <c r="W25" s="25"/>
+      <c r="X25" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="33"/>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="34"/>
-      <c r="AE25" s="34"/>
+      <c r="Y25" s="23"/>
+      <c r="Z25" s="23"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+      <c r="AC25" s="28"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="29"/>
     </row>
     <row r="26" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -3136,14 +3251,18 @@
       <c r="B26" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="D26" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
+      <c r="E26" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G26" s="8" t="s">
         <v>164</v>
       </c>
@@ -3189,7 +3308,7 @@
       <c r="U26" s="11"/>
       <c r="V26" s="11"/>
       <c r="W26" s="10"/>
-      <c r="X26" s="22" t="s">
+      <c r="X26" s="45" t="s">
         <v>167</v>
       </c>
       <c r="Y26" s="8" t="s">
@@ -3210,14 +3329,18 @@
       <c r="B27" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="E27" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G27" s="8" t="s">
         <v>169</v>
       </c>
@@ -3265,7 +3388,7 @@
         <v>25</v>
       </c>
       <c r="W27" s="10"/>
-      <c r="X27" s="23" t="s">
+      <c r="X27" s="46" t="s">
         <v>172</v>
       </c>
       <c r="Y27" s="8" t="s">
@@ -3278,133 +3401,133 @@
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
     </row>
-    <row r="28" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
+    <row r="28" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="8" t="s">
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="9" t="s">
+      <c r="H28" s="23"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="M28" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="N28" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O28" s="9" t="s">
+      <c r="O28" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="P28" s="8" t="s">
+      <c r="P28" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q28" s="10">
+      <c r="Q28" s="25">
         <v>3</v>
       </c>
-      <c r="R28" s="10">
+      <c r="R28" s="25">
         <v>690300</v>
       </c>
-      <c r="S28" s="15">
+      <c r="S28" s="26">
         <v>46082</v>
       </c>
-      <c r="T28" s="8" t="s">
+      <c r="T28" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="U28" s="11"/>
-      <c r="V28" s="8" t="s">
+      <c r="U28" s="27"/>
+      <c r="V28" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="W28" s="10"/>
-      <c r="X28" s="24" t="s">
+      <c r="W28" s="25"/>
+      <c r="X28" s="61" t="s">
         <v>177</v>
       </c>
-      <c r="Y28" s="8" t="s">
+      <c r="Y28" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="Z28" s="8"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="4"/>
-      <c r="AE28" s="4"/>
-    </row>
-    <row r="29" spans="1:31" s="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27">
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="29"/>
+    </row>
+    <row r="29" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="22">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="28" t="s">
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="H29" s="28"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="29" t="s">
+      <c r="H29" s="23"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="M29" s="28" t="s">
+      <c r="M29" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N29" s="28" t="s">
+      <c r="N29" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O29" s="29" t="s">
+      <c r="O29" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="P29" s="28" t="s">
+      <c r="P29" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q29" s="30">
+      <c r="Q29" s="25">
         <v>3</v>
       </c>
-      <c r="R29" s="30">
+      <c r="R29" s="25">
         <v>690300</v>
       </c>
-      <c r="S29" s="31">
+      <c r="S29" s="26">
         <v>46023</v>
       </c>
-      <c r="T29" s="28" t="s">
+      <c r="T29" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="U29" s="32"/>
-      <c r="V29" s="28" t="s">
+      <c r="U29" s="27"/>
+      <c r="V29" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="W29" s="30"/>
-      <c r="X29" s="59" t="s">
+      <c r="W29" s="25"/>
+      <c r="X29" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="Y29" s="28" t="s">
+      <c r="Y29" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="33"/>
-      <c r="AB29" s="33"/>
-      <c r="AC29" s="33"/>
-      <c r="AD29" s="34"/>
-      <c r="AE29" s="34"/>
+      <c r="Z29" s="23"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="29"/>
     </row>
     <row r="30" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
@@ -3414,10 +3537,18 @@
       <c r="B30" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+      <c r="C30" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F30" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G30" s="8" t="s">
         <v>183</v>
       </c>
@@ -3425,7 +3556,7 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
       <c r="K30" s="8"/>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="48" t="s">
         <v>184</v>
       </c>
       <c r="M30" s="8" t="s">
@@ -3457,7 +3588,7 @@
         <v>25</v>
       </c>
       <c r="W30" s="10"/>
-      <c r="X30" s="25" t="s">
+      <c r="X30" s="20" t="s">
         <v>186</v>
       </c>
       <c r="Y30" s="8" t="s">
@@ -3468,7 +3599,7 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="4"/>
-      <c r="AE30" s="26"/>
+      <c r="AE30" s="21"/>
     </row>
     <row r="31" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
@@ -3478,14 +3609,18 @@
       <c r="B31" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D31" s="39" t="s">
+      <c r="D31" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="E31" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G31" s="8" t="s">
         <v>187</v>
       </c>
@@ -3525,7 +3660,7 @@
         <v>25</v>
       </c>
       <c r="W31" s="10"/>
-      <c r="X31" s="25" t="s">
+      <c r="X31" s="20" t="s">
         <v>190</v>
       </c>
       <c r="Y31" s="8" t="s">
@@ -3536,7 +3671,7 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="4"/>
-      <c r="AE31" s="26"/>
+      <c r="AE31" s="21"/>
     </row>
     <row r="32" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
@@ -3546,14 +3681,18 @@
       <c r="B32" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D32" s="56" t="s">
+      <c r="D32" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
+      <c r="E32" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="G32" s="8" t="s">
         <v>191</v>
       </c>
@@ -3593,7 +3732,7 @@
         <v>25</v>
       </c>
       <c r="W32" s="10"/>
-      <c r="X32" s="23" t="s">
+      <c r="X32" s="46" t="s">
         <v>194</v>
       </c>
       <c r="Y32" s="8" t="s">
@@ -3604,7 +3743,7 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="4"/>
-      <c r="AE32" s="26"/>
+      <c r="AE32" s="21"/>
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
@@ -3614,11 +3753,15 @@
       <c r="B33" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="39" t="s">
+      <c r="C33" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="E33" s="13"/>
+      <c r="E33" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="F33" s="13"/>
       <c r="G33" s="8" t="s">
         <v>195</v>
@@ -3659,7 +3802,7 @@
         <v>25</v>
       </c>
       <c r="W33" s="10"/>
-      <c r="X33" s="25" t="s">
+      <c r="X33" s="20" t="s">
         <v>224</v>
       </c>
       <c r="Y33" s="8"/>
@@ -3668,7 +3811,7 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="4"/>
-      <c r="AE33" s="26"/>
+      <c r="AE33" s="21"/>
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
@@ -3678,14 +3821,18 @@
       <c r="B34" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C34" s="39" t="s">
+      <c r="C34" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="D34" s="56" t="s">
+      <c r="D34" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
+      <c r="E34" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="F34" s="34" t="s">
+        <v>219</v>
+      </c>
       <c r="G34" s="8" t="s">
         <v>198</v>
       </c>
@@ -3723,7 +3870,7 @@
         <v>25</v>
       </c>
       <c r="W34" s="10"/>
-      <c r="X34" s="25" t="s">
+      <c r="X34" s="20" t="s">
         <v>201</v>
       </c>
       <c r="Y34" s="8" t="s">
@@ -3735,181 +3882,181 @@
       <c r="AC34" s="1"/>
       <c r="AD34" s="4"/>
     </row>
-    <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13">
+    <row r="35" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="22">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="39" t="s">
+      <c r="C35" s="22"/>
+      <c r="D35" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="8" t="s">
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="H35" s="8"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="9" t="s">
+      <c r="H35" s="23"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="M35" s="8" t="s">
+      <c r="M35" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N35" s="8" t="s">
+      <c r="N35" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="9" t="s">
+      <c r="O35" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="P35" s="8" t="s">
+      <c r="P35" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q35" s="10">
+      <c r="Q35" s="25">
         <v>3</v>
       </c>
-      <c r="R35" s="10"/>
-      <c r="S35" s="11">
+      <c r="R35" s="25"/>
+      <c r="S35" s="27">
         <v>46113</v>
       </c>
-      <c r="T35" s="8" t="s">
+      <c r="T35" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="U35" s="11"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="10"/>
-      <c r="X35" s="25" t="s">
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="Y35" s="8"/>
-      <c r="Z35" s="8"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="26"/>
-    </row>
-    <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="13">
+      <c r="Y35" s="23"/>
+      <c r="Z35" s="23"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
+      <c r="AD35" s="29"/>
+      <c r="AE35" s="63"/>
+    </row>
+    <row r="36" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="22">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="39" t="s">
+      <c r="C36" s="22"/>
+      <c r="D36" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="8" t="s">
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="9" t="s">
+      <c r="H36" s="23"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="M36" s="8" t="s">
+      <c r="M36" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="N36" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O36" s="9" t="s">
+      <c r="O36" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="P36" s="8" t="s">
+      <c r="P36" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q36" s="10">
+      <c r="Q36" s="25">
         <v>3</v>
       </c>
-      <c r="R36" s="10"/>
-      <c r="S36" s="11">
+      <c r="R36" s="25"/>
+      <c r="S36" s="27">
         <v>46113</v>
       </c>
-      <c r="T36" s="8" t="s">
+      <c r="T36" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="U36" s="11"/>
-      <c r="V36" s="11"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="12" t="s">
+      <c r="U36" s="27"/>
+      <c r="V36" s="27"/>
+      <c r="W36" s="25"/>
+      <c r="X36" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="Y36" s="8"/>
-      <c r="Z36" s="8"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-      <c r="AD36" s="4"/>
-    </row>
-    <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
+      <c r="Y36" s="23"/>
+      <c r="Z36" s="23"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
+      <c r="AD36" s="29"/>
+    </row>
+    <row r="37" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="22">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="39" t="s">
+      <c r="C37" s="22"/>
+      <c r="D37" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="8" t="s">
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="9" t="s">
+      <c r="H37" s="23"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="M37" s="8" t="s">
+      <c r="M37" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="N37" s="8" t="s">
+      <c r="N37" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="O37" s="9" t="s">
+      <c r="O37" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="P37" s="8" t="s">
+      <c r="P37" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="Q37" s="10">
+      <c r="Q37" s="25">
         <v>3</v>
       </c>
-      <c r="R37" s="10"/>
-      <c r="S37" s="11">
+      <c r="R37" s="25"/>
+      <c r="S37" s="27">
         <v>46143</v>
       </c>
-      <c r="T37" s="8"/>
-      <c r="U37" s="11"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="12" t="s">
+      <c r="T37" s="23"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="40" t="s">
         <v>228</v>
       </c>
-      <c r="Y37" s="8"/>
-      <c r="Z37" s="8"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="4"/>
+      <c r="Y37" s="23"/>
+      <c r="Z37" s="23"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="29"/>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
@@ -3919,11 +4066,15 @@
       <c r="B38" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="39" t="s">
+      <c r="C38" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="E38" s="13"/>
+      <c r="E38" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="F38" s="13"/>
       <c r="G38" s="8" t="s">
         <v>209</v>
@@ -3970,11 +4121,15 @@
       <c r="B39" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="39" t="s">
+      <c r="C39" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="D39" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="E39" s="13"/>
+      <c r="E39" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="F39" s="13"/>
       <c r="G39" s="8" t="s">
         <v>211</v>
@@ -4003,7 +4158,7 @@
       <c r="U39" s="11"/>
       <c r="V39" s="11"/>
       <c r="W39" s="10"/>
-      <c r="X39" s="25" t="s">
+      <c r="X39" s="20" t="s">
         <v>230</v>
       </c>
       <c r="Y39" s="8"/>
@@ -4012,154 +4167,172 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="4"/>
-      <c r="AE39" s="26"/>
-    </row>
-    <row r="40" spans="1:31" s="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27">
+      <c r="AE39" s="21"/>
+    </row>
+    <row r="40" spans="1:31" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="49">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27" t="s">
+      <c r="B40" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="D40" s="49" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="28" t="s">
+      <c r="E40" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F40" s="49"/>
+      <c r="G40" s="51" t="s">
         <v>213</v>
       </c>
-      <c r="H40" s="28"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="29" t="s">
+      <c r="H40" s="23"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="23"/>
+      <c r="L40" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="M40" s="28" t="s">
+      <c r="M40" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="N40" s="28" t="s">
+      <c r="N40" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="O40" s="29" t="s">
+      <c r="O40" s="53" t="s">
         <v>214</v>
       </c>
-      <c r="P40" s="28" t="s">
+      <c r="P40" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="Q40" s="30">
+      <c r="Q40" s="54">
         <v>3</v>
       </c>
-      <c r="R40" s="30"/>
-      <c r="S40" s="32">
+      <c r="R40" s="54"/>
+      <c r="S40" s="55">
         <v>46029</v>
       </c>
-      <c r="T40" s="28"/>
-      <c r="U40" s="32"/>
-      <c r="V40" s="32"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="60" t="s">
+      <c r="T40" s="51"/>
+      <c r="U40" s="55"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="54"/>
+      <c r="X40" s="56" t="s">
         <v>231</v>
       </c>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="33"/>
-      <c r="AB40" s="33"/>
-      <c r="AC40" s="33"/>
-      <c r="AD40" s="34"/>
-    </row>
-    <row r="41" spans="1:31" s="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="27">
+      <c r="Y40" s="51"/>
+      <c r="Z40" s="51"/>
+      <c r="AA40" s="57"/>
+      <c r="AB40" s="57"/>
+      <c r="AC40" s="57"/>
+      <c r="AD40" s="58"/>
+    </row>
+    <row r="41" spans="1:31" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="49">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B41" s="40" t="s">
+      <c r="B41" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="C41" s="40" t="s">
+      <c r="C41" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="D41" s="40" t="s">
+      <c r="D41" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="E41" s="40" t="s">
+      <c r="E41" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="F41" s="40" t="s">
+      <c r="F41" s="50" t="s">
         <v>238</v>
       </c>
-      <c r="G41" s="28" t="s">
+      <c r="G41" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="H41" s="28"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="29"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="30">
+      <c r="H41" s="23"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="23"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="51"/>
+      <c r="N41" s="51"/>
+      <c r="O41" s="53"/>
+      <c r="P41" s="51"/>
+      <c r="Q41" s="54">
         <v>3</v>
       </c>
-      <c r="R41" s="30"/>
-      <c r="S41" s="32"/>
-      <c r="T41" s="28"/>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
-      <c r="W41" s="30"/>
-      <c r="X41" s="60" t="s">
+      <c r="R41" s="54"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="51"/>
+      <c r="U41" s="55"/>
+      <c r="V41" s="55"/>
+      <c r="W41" s="54"/>
+      <c r="X41" s="56" t="s">
         <v>232</v>
       </c>
-      <c r="Y41" s="28"/>
-      <c r="Z41" s="28"/>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
-      <c r="AD41" s="34"/>
-    </row>
-    <row r="42" spans="1:31" s="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27">
+      <c r="Y41" s="51"/>
+      <c r="Z41" s="51"/>
+      <c r="AA41" s="57"/>
+      <c r="AB41" s="57"/>
+      <c r="AC41" s="57"/>
+      <c r="AD41" s="58"/>
+    </row>
+    <row r="42" spans="1:31" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="49">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="28" t="s">
+      <c r="B42" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="D42" s="49" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F42" s="49"/>
+      <c r="G42" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="H42" s="28"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="29"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="29"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="30">
+      <c r="H42" s="23"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="M42" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="N42" s="51"/>
+      <c r="O42" s="53"/>
+      <c r="P42" s="51"/>
+      <c r="Q42" s="54">
         <v>3</v>
       </c>
-      <c r="R42" s="30"/>
-      <c r="S42" s="32"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="32"/>
-      <c r="V42" s="32"/>
-      <c r="W42" s="30"/>
-      <c r="X42" s="60" t="s">
+      <c r="R42" s="54"/>
+      <c r="S42" s="55"/>
+      <c r="T42" s="51"/>
+      <c r="U42" s="55"/>
+      <c r="V42" s="55"/>
+      <c r="W42" s="54"/>
+      <c r="X42" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
-      <c r="AD42" s="34"/>
+      <c r="Y42" s="51"/>
+      <c r="Z42" s="51"/>
+      <c r="AA42" s="57"/>
+      <c r="AB42" s="57"/>
+      <c r="AC42" s="57"/>
+      <c r="AD42" s="58"/>
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
@@ -35133,7 +35306,7 @@
     <hyperlink ref="X34" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId56"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId56"/>
+  <legacyDrawing r:id="rId57"/>
 </worksheet>
 </file>
--- a/src/Thông tin HKD.xlsx
+++ b/src/Thông tin HKD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEVELOPER\3.accounting_excel\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D70D98-D50F-4418-B349-32076591BE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF33FCA-3D19-4A88-8FC4-6DCEE9E8C66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="242">
   <si>
     <t>STT</t>
   </si>
@@ -864,6 +864,9 @@
   <si>
     <t>066194015688</t>
   </si>
+  <si>
+    <t>~</t>
+  </si>
 </sst>
 </file>
 
@@ -1042,7 +1045,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1110,25 +1113,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1344,6 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE1008"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1377,11 +1368,11 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1">
         <f>COUNTIF(E$4:E$42,"v")</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1">
         <f>COUNTIF(F$4:F$42,"v")</f>
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1417,11 +1408,11 @@
       </c>
       <c r="E2" s="47">
         <f>E1/(MAX($A$4:$A$42)-COUNTIF(E$4:E$42,"-"))</f>
-        <v>0.7567567567567568</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="F2" s="47">
         <f>F1/(MAX($A$4:$A$42)-COUNTIF(F$4:F$42,"-"))</f>
-        <v>0.6216216216216216</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1532,7 +1523,7 @@
       <c r="AC3" s="6"/>
       <c r="AD3" s="7"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -1619,9 +1610,15 @@
       <c r="B5" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
+      <c r="C5" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="F5" s="22"/>
       <c r="G5" s="23" t="s">
         <v>28</v>
@@ -1638,7 +1635,7 @@
       <c r="K5" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="24" t="s">
+      <c r="L5" s="54" t="s">
         <v>30</v>
       </c>
       <c r="M5" s="23" t="s">
@@ -1683,7 +1680,7 @@
       <c r="AD5" s="29"/>
       <c r="AE5" s="29"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1763,7 +1760,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1841,7 +1838,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1921,7 +1918,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1993,7 +1990,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2001,10 +1998,18 @@
       <c r="B10" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
+      <c r="C10" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="G10" s="23" t="s">
         <v>63</v>
       </c>
@@ -2020,7 +2025,7 @@
       <c r="K10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="24" t="s">
+      <c r="L10" s="54" t="s">
         <v>65</v>
       </c>
       <c r="M10" s="23" t="s">
@@ -2063,7 +2068,7 @@
       <c r="AD10" s="29"/>
       <c r="AE10" s="29"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2143,7 +2148,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2223,7 +2228,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2303,7 +2308,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2383,7 +2388,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2463,7 +2468,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2558,11 +2563,9 @@
         <v>219</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="F17" s="35" t="s">
-        <v>238</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="F17" s="35"/>
       <c r="G17" s="23" t="s">
         <v>112</v>
       </c>
@@ -2578,7 +2581,7 @@
       <c r="K17" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="24" t="s">
+      <c r="L17" s="54" t="s">
         <v>114</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -2623,7 +2626,7 @@
       <c r="AD17" s="29"/>
       <c r="AE17" s="29"/>
     </row>
-    <row r="18" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2703,7 +2706,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
     </row>
-    <row r="19" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" s="30" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2711,10 +2714,18 @@
       <c r="B19" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
+      <c r="C19" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F19" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="G19" s="23" t="s">
         <v>125</v>
       </c>
@@ -2775,7 +2786,7 @@
       <c r="AD19" s="29"/>
       <c r="AE19" s="29"/>
     </row>
-    <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2855,7 +2866,7 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
     </row>
-    <row r="21" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2933,7 +2944,7 @@
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
     </row>
-    <row r="22" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3013,7 +3024,7 @@
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
     </row>
-    <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3093,7 +3104,7 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
     </row>
-    <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3243,7 +3254,7 @@
       <c r="AD25" s="29"/>
       <c r="AE25" s="29"/>
     </row>
-    <row r="26" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3321,7 +3332,7 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
     </row>
-    <row r="27" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3409,8 +3420,12 @@
       <c r="B28" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
+      <c r="C28" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>241</v>
+      </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="23" t="s">
@@ -3452,7 +3467,7 @@
         <v>25</v>
       </c>
       <c r="W28" s="25"/>
-      <c r="X28" s="61" t="s">
+      <c r="X28" s="51" t="s">
         <v>177</v>
       </c>
       <c r="Y28" s="23" t="s">
@@ -3529,7 +3544,7 @@
       <c r="AD29" s="29"/>
       <c r="AE29" s="29"/>
     </row>
-    <row r="30" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3601,7 +3616,7 @@
       <c r="AD30" s="4"/>
       <c r="AE30" s="21"/>
     </row>
-    <row r="31" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3673,7 +3688,7 @@
       <c r="AD31" s="4"/>
       <c r="AE31" s="21"/>
     </row>
-    <row r="32" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3745,7 +3760,7 @@
       <c r="AD32" s="4"/>
       <c r="AE32" s="21"/>
     </row>
-    <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3762,7 +3777,9 @@
       <c r="E33" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F33" s="13"/>
+      <c r="F33" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="G33" s="8" t="s">
         <v>195</v>
       </c>
@@ -3813,7 +3830,7 @@
       <c r="AD33" s="4"/>
       <c r="AE33" s="21"/>
     </row>
-    <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3931,7 +3948,7 @@
       <c r="U35" s="27"/>
       <c r="V35" s="27"/>
       <c r="W35" s="25"/>
-      <c r="X35" s="62" t="s">
+      <c r="X35" s="52" t="s">
         <v>226</v>
       </c>
       <c r="Y35" s="23"/>
@@ -3940,7 +3957,7 @@
       <c r="AB35" s="28"/>
       <c r="AC35" s="28"/>
       <c r="AD35" s="29"/>
-      <c r="AE35" s="63"/>
+      <c r="AE35" s="53"/>
     </row>
     <row r="36" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22">
@@ -4058,7 +4075,7 @@
       <c r="AC37" s="28"/>
       <c r="AD37" s="29"/>
     </row>
-    <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -4075,7 +4092,9 @@
       <c r="E38" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F38" s="13"/>
+      <c r="F38" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="G38" s="8" t="s">
         <v>209</v>
       </c>
@@ -4113,7 +4132,7 @@
       <c r="AC38" s="1"/>
       <c r="AD38" s="4"/>
     </row>
-    <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -4130,7 +4149,9 @@
       <c r="E39" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>219</v>
+      </c>
       <c r="G39" s="8" t="s">
         <v>211</v>
       </c>
@@ -4169,170 +4190,174 @@
       <c r="AD39" s="4"/>
       <c r="AE39" s="21"/>
     </row>
-    <row r="40" spans="1:31" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="49">
+    <row r="40" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B40" s="50" t="s">
+      <c r="B40" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="49" t="s">
+      <c r="C40" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D40" s="49" t="s">
+      <c r="D40" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E40" s="49" t="s">
+      <c r="E40" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F40" s="49"/>
-      <c r="G40" s="51" t="s">
+      <c r="F40" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>213</v>
       </c>
       <c r="H40" s="23"/>
       <c r="I40" s="22"/>
       <c r="J40" s="22"/>
       <c r="K40" s="23"/>
-      <c r="L40" s="53" t="s">
+      <c r="L40" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="M40" s="51" t="s">
+      <c r="M40" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N40" s="51" t="s">
+      <c r="N40" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="O40" s="53" t="s">
+      <c r="O40" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="P40" s="51" t="s">
+      <c r="P40" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="Q40" s="54">
+      <c r="Q40" s="10">
         <v>3</v>
       </c>
-      <c r="R40" s="54"/>
-      <c r="S40" s="55">
+      <c r="R40" s="10"/>
+      <c r="S40" s="11">
         <v>46029</v>
       </c>
-      <c r="T40" s="51"/>
-      <c r="U40" s="55"/>
-      <c r="V40" s="55"/>
-      <c r="W40" s="54"/>
-      <c r="X40" s="56" t="s">
+      <c r="T40" s="8"/>
+      <c r="U40" s="11"/>
+      <c r="V40" s="11"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="Y40" s="51"/>
-      <c r="Z40" s="51"/>
-      <c r="AA40" s="57"/>
-      <c r="AB40" s="57"/>
-      <c r="AC40" s="57"/>
-      <c r="AD40" s="58"/>
-    </row>
-    <row r="41" spans="1:31" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="49">
+      <c r="Y40" s="8"/>
+      <c r="Z40" s="8"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="4"/>
+    </row>
+    <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="E41" s="50" t="s">
+      <c r="E41" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="F41" s="50" t="s">
+      <c r="F41" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="G41" s="51" t="s">
+      <c r="G41" s="8" t="s">
         <v>215</v>
       </c>
       <c r="H41" s="23"/>
       <c r="I41" s="22"/>
       <c r="J41" s="22"/>
       <c r="K41" s="23"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="53"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="54">
+      <c r="L41" s="9"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="8"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="8"/>
+      <c r="Q41" s="10">
         <v>3</v>
       </c>
-      <c r="R41" s="54"/>
-      <c r="S41" s="55"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="55"/>
-      <c r="V41" s="55"/>
-      <c r="W41" s="54"/>
-      <c r="X41" s="56" t="s">
+      <c r="R41" s="10"/>
+      <c r="S41" s="11"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="10"/>
+      <c r="X41" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="Y41" s="51"/>
-      <c r="Z41" s="51"/>
-      <c r="AA41" s="57"/>
-      <c r="AB41" s="57"/>
-      <c r="AC41" s="57"/>
-      <c r="AD41" s="58"/>
-    </row>
-    <row r="42" spans="1:31" s="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="49">
+      <c r="Y41" s="8"/>
+      <c r="Z41" s="8"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="4"/>
+    </row>
+    <row r="42" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C42" s="49" t="s">
+      <c r="C42" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="D42" s="49" t="s">
+      <c r="D42" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="E42" s="49" t="s">
+      <c r="E42" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="F42" s="49"/>
-      <c r="G42" s="52" t="s">
+      <c r="F42" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="G42" s="49" t="s">
         <v>216</v>
       </c>
       <c r="H42" s="23"/>
       <c r="I42" s="22"/>
       <c r="J42" s="22"/>
       <c r="K42" s="23"/>
-      <c r="L42" s="60" t="s">
+      <c r="L42" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="M42" s="51" t="s">
+      <c r="M42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N42" s="51"/>
-      <c r="O42" s="53"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="54">
+      <c r="N42" s="8"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="8"/>
+      <c r="Q42" s="10">
         <v>3</v>
       </c>
-      <c r="R42" s="54"/>
-      <c r="S42" s="55"/>
-      <c r="T42" s="51"/>
-      <c r="U42" s="55"/>
-      <c r="V42" s="55"/>
-      <c r="W42" s="54"/>
-      <c r="X42" s="56" t="s">
+      <c r="R42" s="10"/>
+      <c r="S42" s="11"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="11"/>
+      <c r="V42" s="11"/>
+      <c r="W42" s="10"/>
+      <c r="X42" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="Y42" s="51"/>
-      <c r="Z42" s="51"/>
-      <c r="AA42" s="57"/>
-      <c r="AB42" s="57"/>
-      <c r="AC42" s="57"/>
-      <c r="AD42" s="58"/>
+      <c r="Y42" s="8"/>
+      <c r="Z42" s="8"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="4"/>
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
@@ -35247,7 +35272,13 @@
       <c r="AD1008" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Z42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:Z42" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <filters blank="1">
+        <filter val="-"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/src/Thông tin HKD.xlsx
+++ b/src/Thông tin HKD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEVELOPER\3.accounting_excel\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF33FCA-3D19-4A88-8FC4-6DCEE9E8C66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDA9A88-EAAE-47A0-8E71-1CADBBE472BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,7 +140,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="241">
   <si>
     <t>STT</t>
   </si>
@@ -864,9 +864,6 @@
   <si>
     <t>066194015688</t>
   </si>
-  <si>
-    <t>~</t>
-  </si>
 </sst>
 </file>
 
@@ -1368,11 +1365,11 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1">
         <f>COUNTIF(E$4:E$42,"v")</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1">
         <f>COUNTIF(F$4:F$42,"v")</f>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1408,11 +1405,11 @@
       </c>
       <c r="E2" s="47">
         <f>E1/(MAX($A$4:$A$42)-COUNTIF(E$4:E$42,"-"))</f>
-        <v>0.84210526315789469</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="F2" s="47">
         <f>F1/(MAX($A$4:$A$42)-COUNTIF(F$4:F$42,"-"))</f>
-        <v>0.78947368421052633</v>
+        <v>0.86842105263157898</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1602,7 +1599,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <f t="shared" ref="A5:A42" si="0">+A4+1</f>
         <v>2</v>
@@ -1619,7 +1616,9 @@
       <c r="E5" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="F5" s="22"/>
+      <c r="F5" s="22" t="s">
+        <v>219</v>
+      </c>
       <c r="G5" s="23" t="s">
         <v>28</v>
       </c>
@@ -2548,7 +2547,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2565,7 +2564,9 @@
       <c r="E17" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="F17" s="35"/>
+      <c r="F17" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="G17" s="23" t="s">
         <v>112</v>
       </c>
@@ -3412,7 +3413,7 @@
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
     </row>
-    <row r="28" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" s="30" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3421,13 +3422,17 @@
         <v>219</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
+        <v>219</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F28" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="G28" s="23" t="s">
         <v>174</v>
       </c>
@@ -3907,11 +3912,15 @@
       <c r="B35" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C35" s="22"/>
+      <c r="C35" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="D35" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="E35" s="22"/>
+      <c r="E35" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="F35" s="22"/>
       <c r="G35" s="23" t="s">
         <v>202</v>
@@ -3920,7 +3929,7 @@
       <c r="I35" s="22"/>
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
-      <c r="L35" s="24" t="s">
+      <c r="L35" s="54" t="s">
         <v>203</v>
       </c>
       <c r="M35" s="23" t="s">
@@ -3967,11 +3976,15 @@
       <c r="B36" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C36" s="22"/>
+      <c r="C36" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="D36" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="E36" s="22"/>
+      <c r="E36" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="F36" s="22"/>
       <c r="G36" s="23" t="s">
         <v>205</v>
@@ -3980,7 +3993,7 @@
       <c r="I36" s="22"/>
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
-      <c r="L36" s="24" t="s">
+      <c r="L36" s="54" t="s">
         <v>206</v>
       </c>
       <c r="M36" s="23" t="s">
@@ -4026,11 +4039,15 @@
       <c r="B37" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="22"/>
+      <c r="C37" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="D37" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="E37" s="22"/>
+      <c r="E37" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="F37" s="22"/>
       <c r="G37" s="23" t="s">
         <v>207</v>
@@ -4039,7 +4056,7 @@
       <c r="I37" s="22"/>
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
-      <c r="L37" s="24" t="s">
+      <c r="L37" s="54" t="s">
         <v>208</v>
       </c>
       <c r="M37" s="23" t="s">

--- a/src/Thông tin HKD.xlsx
+++ b/src/Thông tin HKD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEVELOPER\3.accounting_excel\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDA9A88-EAAE-47A0-8E71-1CADBBE472BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C048B80D-5E31-405A-8438-A31CC0D53858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -106,6 +106,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="F25" authorId="1" shapeId="0" xr:uid="{EFF90B35-07F8-42D4-ACEE-866B820854C3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Cường làm</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C42" authorId="1" shapeId="0" xr:uid="{03672AE1-88CC-4081-AE40-7760DEC91C87}">
       <text>
         <r>
@@ -140,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="241">
   <si>
     <t>STT</t>
   </si>
@@ -1042,7 +1066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1113,9 +1137,24 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1331,7 +1370,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AE1008"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1365,11 +1403,11 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1">
         <f>COUNTIF(E$4:E$42,"v")</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1">
         <f>COUNTIF(F$4:F$42,"v")</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1405,11 +1443,11 @@
       </c>
       <c r="E2" s="47">
         <f>E1/(MAX($A$4:$A$42)-COUNTIF(E$4:E$42,"-"))</f>
-        <v>0.94736842105263153</v>
+        <v>1</v>
       </c>
       <c r="F2" s="47">
         <f>F1/(MAX($A$4:$A$42)-COUNTIF(F$4:F$42,"-"))</f>
-        <v>0.86842105263157898</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1520,7 +1558,7 @@
       <c r="AC3" s="6"/>
       <c r="AD3" s="7"/>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>1</v>
       </c>
@@ -1599,7 +1637,7 @@
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
     </row>
-    <row r="5" spans="1:31" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="22">
         <f t="shared" ref="A5:A42" si="0">+A4+1</f>
         <v>2</v>
@@ -1634,7 +1672,7 @@
       <c r="K5" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="54" t="s">
+      <c r="L5" s="52" t="s">
         <v>30</v>
       </c>
       <c r="M5" s="23" t="s">
@@ -1679,7 +1717,7 @@
       <c r="AD5" s="29"/>
       <c r="AE5" s="29"/>
     </row>
-    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1759,7 +1797,7 @@
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
     </row>
-    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1837,7 +1875,7 @@
       <c r="AD7" s="4"/>
       <c r="AE7" s="4"/>
     </row>
-    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1917,7 +1955,7 @@
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
     </row>
-    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1989,7 +2027,7 @@
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
     </row>
-    <row r="10" spans="1:31" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2024,7 +2062,7 @@
       <c r="K10" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="54" t="s">
+      <c r="L10" s="52" t="s">
         <v>65</v>
       </c>
       <c r="M10" s="23" t="s">
@@ -2067,7 +2105,7 @@
       <c r="AD10" s="29"/>
       <c r="AE10" s="29"/>
     </row>
-    <row r="11" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2147,7 +2185,7 @@
       <c r="AD11" s="4"/>
       <c r="AE11" s="4"/>
     </row>
-    <row r="12" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2227,7 +2265,7 @@
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
     </row>
-    <row r="13" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2307,7 +2345,7 @@
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
     </row>
-    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2387,7 +2425,7 @@
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
     </row>
-    <row r="15" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2467,7 +2505,7 @@
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
     </row>
-    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2547,7 +2585,7 @@
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
     </row>
-    <row r="17" spans="1:31" s="30" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="22">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2582,7 +2620,7 @@
       <c r="K17" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L17" s="54" t="s">
+      <c r="L17" s="52" t="s">
         <v>114</v>
       </c>
       <c r="M17" s="23" t="s">
@@ -2627,7 +2665,7 @@
       <c r="AD17" s="29"/>
       <c r="AE17" s="29"/>
     </row>
-    <row r="18" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2707,7 +2745,7 @@
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
     </row>
-    <row r="19" spans="1:31" s="30" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="22">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2787,7 +2825,7 @@
       <c r="AD19" s="29"/>
       <c r="AE19" s="29"/>
     </row>
-    <row r="20" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2867,7 +2905,7 @@
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
     </row>
-    <row r="21" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2945,7 +2983,7 @@
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
     </row>
-    <row r="22" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3025,7 +3063,7 @@
       <c r="AD22" s="4"/>
       <c r="AE22" s="4"/>
     </row>
-    <row r="23" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3105,7 +3143,7 @@
       <c r="AD23" s="4"/>
       <c r="AE23" s="4"/>
     </row>
-    <row r="24" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3191,12 +3229,20 @@
         <v>22</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
+        <v>238</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>238</v>
+      </c>
       <c r="G25" s="23" t="s">
         <v>160</v>
       </c>
@@ -3255,7 +3301,7 @@
       <c r="AD25" s="29"/>
       <c r="AE25" s="29"/>
     </row>
-    <row r="26" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3333,7 +3379,7 @@
       <c r="AD26" s="4"/>
       <c r="AE26" s="4"/>
     </row>
-    <row r="27" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3413,7 +3459,7 @@
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
     </row>
-    <row r="28" spans="1:31" s="30" customFormat="1" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="22">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3493,10 +3539,18 @@
       <c r="B29" s="22" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
+      <c r="C29" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="F29" s="35" t="s">
+        <v>219</v>
+      </c>
       <c r="G29" s="23" t="s">
         <v>179</v>
       </c>
@@ -3549,7 +3603,7 @@
       <c r="AD29" s="29"/>
       <c r="AE29" s="29"/>
     </row>
-    <row r="30" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3621,7 +3675,7 @@
       <c r="AD30" s="4"/>
       <c r="AE30" s="21"/>
     </row>
-    <row r="31" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3693,7 +3747,7 @@
       <c r="AD31" s="4"/>
       <c r="AE31" s="21"/>
     </row>
-    <row r="32" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3765,7 +3819,7 @@
       <c r="AD32" s="4"/>
       <c r="AE32" s="21"/>
     </row>
-    <row r="33" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3835,7 +3889,7 @@
       <c r="AD33" s="4"/>
       <c r="AE33" s="21"/>
     </row>
-    <row r="34" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3904,69 +3958,71 @@
       <c r="AC34" s="1"/>
       <c r="AD34" s="4"/>
     </row>
-    <row r="35" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22">
+    <row r="35" spans="1:31" s="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="53">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="F35" s="22"/>
-      <c r="G35" s="23" t="s">
+      <c r="F35" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" s="55" t="s">
         <v>202</v>
       </c>
       <c r="H35" s="23"/>
       <c r="I35" s="22"/>
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
-      <c r="L35" s="54" t="s">
+      <c r="L35" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="M35" s="23" t="s">
+      <c r="M35" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="N35" s="23" t="s">
+      <c r="N35" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="O35" s="24" t="s">
+      <c r="O35" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="P35" s="23" t="s">
+      <c r="P35" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="Q35" s="25">
+      <c r="Q35" s="58">
         <v>3</v>
       </c>
-      <c r="R35" s="25"/>
-      <c r="S35" s="27">
+      <c r="R35" s="58"/>
+      <c r="S35" s="59">
         <v>46113</v>
       </c>
-      <c r="T35" s="23" t="s">
+      <c r="T35" s="55" t="s">
         <v>204</v>
       </c>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="52" t="s">
+      <c r="U35" s="59"/>
+      <c r="V35" s="59"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="60" t="s">
         <v>226</v>
       </c>
-      <c r="Y35" s="23"/>
-      <c r="Z35" s="23"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
-      <c r="AD35" s="29"/>
-      <c r="AE35" s="53"/>
+      <c r="Y35" s="55"/>
+      <c r="Z35" s="55"/>
+      <c r="AA35" s="61"/>
+      <c r="AB35" s="61"/>
+      <c r="AC35" s="61"/>
+      <c r="AD35" s="62"/>
+      <c r="AE35" s="63"/>
     </row>
     <row r="36" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="22">
@@ -3985,7 +4041,9 @@
       <c r="E36" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="F36" s="22"/>
+      <c r="F36" s="22" t="s">
+        <v>219</v>
+      </c>
       <c r="G36" s="23" t="s">
         <v>205</v>
       </c>
@@ -3993,7 +4051,7 @@
       <c r="I36" s="22"/>
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
-      <c r="L36" s="54" t="s">
+      <c r="L36" s="52" t="s">
         <v>206</v>
       </c>
       <c r="M36" s="23" t="s">
@@ -4031,68 +4089,70 @@
       <c r="AC36" s="28"/>
       <c r="AD36" s="29"/>
     </row>
-    <row r="37" spans="1:31" s="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="22">
+    <row r="37" spans="1:31" s="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="53">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="53" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="E37" s="35" t="s">
+      <c r="E37" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="F37" s="22"/>
-      <c r="G37" s="23" t="s">
+      <c r="F37" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="55" t="s">
         <v>207</v>
       </c>
       <c r="H37" s="23"/>
       <c r="I37" s="22"/>
       <c r="J37" s="22"/>
       <c r="K37" s="23"/>
-      <c r="L37" s="54" t="s">
+      <c r="L37" s="56" t="s">
         <v>208</v>
       </c>
-      <c r="M37" s="23" t="s">
+      <c r="M37" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="N37" s="23" t="s">
+      <c r="N37" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="O37" s="24" t="s">
+      <c r="O37" s="57" t="s">
         <v>208</v>
       </c>
-      <c r="P37" s="23" t="s">
+      <c r="P37" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="Q37" s="25">
+      <c r="Q37" s="58">
         <v>3</v>
       </c>
-      <c r="R37" s="25"/>
-      <c r="S37" s="27">
+      <c r="R37" s="58"/>
+      <c r="S37" s="59">
         <v>46143</v>
       </c>
-      <c r="T37" s="23"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="40" t="s">
+      <c r="T37" s="55"/>
+      <c r="U37" s="59"/>
+      <c r="V37" s="59"/>
+      <c r="W37" s="58"/>
+      <c r="X37" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="Y37" s="23"/>
-      <c r="Z37" s="23"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="29"/>
-    </row>
-    <row r="38" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y37" s="55"/>
+      <c r="Z37" s="55"/>
+      <c r="AA37" s="61"/>
+      <c r="AB37" s="61"/>
+      <c r="AC37" s="61"/>
+      <c r="AD37" s="62"/>
+    </row>
+    <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -4149,7 +4209,7 @@
       <c r="AC38" s="1"/>
       <c r="AD38" s="4"/>
     </row>
-    <row r="39" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -4207,7 +4267,7 @@
       <c r="AD39" s="4"/>
       <c r="AE39" s="21"/>
     </row>
-    <row r="40" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -4321,7 +4381,7 @@
       <c r="AC41" s="1"/>
       <c r="AD41" s="4"/>
     </row>
-    <row r="42" spans="1:31" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -35289,13 +35349,7 @@
       <c r="AD1008" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Z42" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters blank="1">
-        <filter val="-"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:Z42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="H4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
